--- a/huge数据对比/3mz-vs-jacky.xlsx
+++ b/huge数据对比/3mz-vs-jacky.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\best igl wiki\huge数据对比\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CCE625B-1259-4496-BE74-7AC41269A08D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB83238F-06E5-4069-8360-0D6D70D6535C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-31087" yWindow="-109" windowWidth="31196" windowHeight="18974" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -214,7 +215,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -250,6 +251,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="184" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -542,11 +546,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
       <c r="D1" s="9" t="s">
         <v>0</v>
       </c>
@@ -602,11 +606,11 @@
       <c r="AB1" s="9"/>
     </row>
     <row r="2" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
       <c r="D2" s="9" t="s">
         <v>19</v>
       </c>
@@ -665,9 +669,9 @@
       <c r="AB2" s="9"/>
     </row>
     <row r="3" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
       <c r="D3" s="9" t="s">
         <v>2</v>
       </c>
@@ -726,9 +730,9 @@
       <c r="AB3" s="9"/>
     </row>
     <row r="4" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
       <c r="D4" s="9" t="s">
         <v>20</v>
       </c>
@@ -797,9 +801,9 @@
       <c r="AB4" s="9"/>
     </row>
     <row r="5" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
       <c r="D5" s="9" t="s">
         <v>23</v>
       </c>
@@ -855,9 +859,9 @@
       <c r="AB5" s="9"/>
     </row>
     <row r="6" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
       <c r="D6" s="9" t="s">
         <v>28</v>
       </c>
@@ -920,9 +924,9 @@
       <c r="AB6" s="9"/>
     </row>
     <row r="7" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
       <c r="D7" s="9" t="s">
         <v>29</v>
       </c>
@@ -985,9 +989,9 @@
       <c r="AB7" s="9"/>
     </row>
     <row r="8" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
       <c r="D8" s="9" t="s">
         <v>22</v>
       </c>
@@ -1056,11 +1060,11 @@
       <c r="AB8" s="9"/>
     </row>
     <row r="9" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
       <c r="D9" s="1" t="s">
         <v>0</v>
       </c>
@@ -1116,11 +1120,11 @@
       <c r="AB9" s="1"/>
     </row>
     <row r="10" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
       <c r="D10" s="9" t="s">
         <v>19</v>
       </c>
@@ -1179,9 +1183,9 @@
       <c r="AB10" s="1"/>
     </row>
     <row r="11" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
       <c r="D11" s="9" t="s">
         <v>2</v>
       </c>
@@ -1240,9 +1244,9 @@
       <c r="AB11" s="1"/>
     </row>
     <row r="12" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
+      <c r="A12" s="13"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
       <c r="D12" s="9" t="s">
         <v>20</v>
       </c>
@@ -1311,9 +1315,9 @@
       <c r="AB12" s="1"/>
     </row>
     <row r="13" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
       <c r="D13" s="9" t="s">
         <v>23</v>
       </c>
@@ -1369,9 +1373,9 @@
       <c r="AB13" s="9"/>
     </row>
     <row r="14" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
+      <c r="A14" s="13"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
       <c r="D14" s="9" t="s">
         <v>30</v>
       </c>
@@ -1434,9 +1438,9 @@
       <c r="AB14" s="9"/>
     </row>
     <row r="15" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
       <c r="D15" s="9" t="s">
         <v>29</v>
       </c>
@@ -1499,9 +1503,9 @@
       <c r="AB15" s="9"/>
     </row>
     <row r="16" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
       <c r="D16" s="9" t="s">
         <v>22</v>
       </c>
@@ -1570,11 +1574,11 @@
       <c r="AB16" s="9"/>
     </row>
     <row r="17" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
       <c r="D17" s="9" t="s">
         <v>0</v>
       </c>
@@ -1630,11 +1634,11 @@
       <c r="AB17" s="1"/>
     </row>
     <row r="18" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
       <c r="D18" s="9" t="s">
         <v>19</v>
       </c>
@@ -1693,9 +1697,9 @@
       <c r="AB18" s="1"/>
     </row>
     <row r="19" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
       <c r="D19" s="9" t="s">
         <v>2</v>
       </c>
@@ -1754,9 +1758,9 @@
       <c r="AB19" s="1"/>
     </row>
     <row r="20" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
       <c r="D20" s="9" t="s">
         <v>20</v>
       </c>
@@ -1825,9 +1829,9 @@
       <c r="AB20" s="1"/>
     </row>
     <row r="21" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
       <c r="D21" s="9" t="s">
         <v>23</v>
       </c>
@@ -1883,9 +1887,9 @@
       <c r="AB21" s="9"/>
     </row>
     <row r="22" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="10"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
       <c r="D22" s="9" t="s">
         <v>32</v>
       </c>
@@ -1948,9 +1952,9 @@
       <c r="AB22" s="9"/>
     </row>
     <row r="23" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="10"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
+      <c r="A23" s="13"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
       <c r="D23" s="9" t="s">
         <v>31</v>
       </c>
@@ -2013,9 +2017,9 @@
       <c r="AB23" s="9"/>
     </row>
     <row r="24" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="10"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
+      <c r="A24" s="13"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
       <c r="D24" s="9" t="s">
         <v>27</v>
       </c>
@@ -2028,7 +2032,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="2">
-        <f t="shared" ref="F24:I24" si="28">G22-G23</f>
+        <f t="shared" ref="G24:I24" si="28">G22-G23</f>
         <v>-20</v>
       </c>
       <c r="H24" s="2">
@@ -2084,11 +2088,11 @@
       <c r="AB24" s="9"/>
     </row>
     <row r="25" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
       <c r="D25" s="1" t="s">
         <v>0</v>
       </c>
@@ -2144,11 +2148,11 @@
       <c r="AB25" s="1"/>
     </row>
     <row r="26" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
       <c r="D26" s="9" t="s">
         <v>19</v>
       </c>
@@ -2207,9 +2211,9 @@
       <c r="AB26" s="1"/>
     </row>
     <row r="27" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
+      <c r="A27" s="13"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
       <c r="D27" s="9" t="s">
         <v>2</v>
       </c>
@@ -2268,9 +2272,9 @@
       <c r="AB27" s="1"/>
     </row>
     <row r="28" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
+      <c r="A28" s="13"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
       <c r="D28" s="9" t="s">
         <v>20</v>
       </c>
@@ -2339,9 +2343,9 @@
       <c r="AB28" s="1"/>
     </row>
     <row r="29" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
+      <c r="A29" s="13"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
       <c r="D29" s="9" t="s">
         <v>23</v>
       </c>
@@ -2397,9 +2401,9 @@
       <c r="AB29" s="9"/>
     </row>
     <row r="30" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
       <c r="D30" s="9" t="s">
         <v>33</v>
       </c>
@@ -2462,9 +2466,9 @@
       <c r="AB30" s="9"/>
     </row>
     <row r="31" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
+      <c r="A31" s="13"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
       <c r="D31" s="9" t="s">
         <v>31</v>
       </c>
@@ -2527,9 +2531,9 @@
       <c r="AB31" s="9"/>
     </row>
     <row r="32" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="10"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
+      <c r="A32" s="13"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
       <c r="D32" s="9" t="s">
         <v>27</v>
       </c>
@@ -2542,7 +2546,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="2">
-        <f t="shared" ref="G32:J32" si="43">G30-G31</f>
+        <f t="shared" ref="G32:I32" si="43">G30-G31</f>
         <v>1</v>
       </c>
       <c r="H32" s="2">
@@ -2598,9 +2602,9 @@
       <c r="AB32" s="9"/>
     </row>
     <row r="33" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
+      <c r="A33" s="13"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
@@ -2628,9 +2632,9 @@
       <c r="AB33" s="9"/>
     </row>
     <row r="34" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="10"/>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
+      <c r="A34" s="13"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
@@ -2658,9 +2662,9 @@
       <c r="AB34" s="9"/>
     </row>
     <row r="35" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
+      <c r="A35" s="13"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
       <c r="D35" s="9"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
@@ -2688,9 +2692,9 @@
       <c r="AB35" s="9"/>
     </row>
     <row r="36" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="10"/>
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
+      <c r="A36" s="13"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9"/>
@@ -2718,9 +2722,9 @@
       <c r="AB36" s="9"/>
     </row>
     <row r="37" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="10"/>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
+      <c r="A37" s="13"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9"/>
@@ -2748,9 +2752,9 @@
       <c r="AB37" s="9"/>
     </row>
     <row r="38" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="10"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
+      <c r="A38" s="13"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
@@ -2778,9 +2782,9 @@
       <c r="AB38" s="9"/>
     </row>
     <row r="39" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="10"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
+      <c r="A39" s="13"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
       <c r="D39" s="9"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
@@ -2808,9 +2812,9 @@
       <c r="AB39" s="9"/>
     </row>
     <row r="40" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="10"/>
-      <c r="B40" s="10"/>
-      <c r="C40" s="10"/>
+      <c r="A40" s="13"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13"/>
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
       <c r="F40" s="9"/>
@@ -2868,9 +2872,9 @@
       <c r="AB41" s="9"/>
     </row>
     <row r="42" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="10"/>
-      <c r="B42" s="10"/>
-      <c r="C42" s="10"/>
+      <c r="A42" s="13"/>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13"/>
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
@@ -2898,9 +2902,9 @@
       <c r="AB42" s="9"/>
     </row>
     <row r="43" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="10"/>
-      <c r="B43" s="10"/>
-      <c r="C43" s="10"/>
+      <c r="A43" s="13"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
       <c r="F43" s="9"/>
@@ -2928,9 +2932,9 @@
       <c r="AB43" s="9"/>
     </row>
     <row r="44" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="10"/>
-      <c r="B44" s="10"/>
-      <c r="C44" s="10"/>
+      <c r="A44" s="13"/>
+      <c r="B44" s="13"/>
+      <c r="C44" s="13"/>
       <c r="D44" s="9"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
@@ -2958,9 +2962,9 @@
       <c r="AB44" s="9"/>
     </row>
     <row r="45" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="10"/>
-      <c r="B45" s="10"/>
-      <c r="C45" s="10"/>
+      <c r="A45" s="13"/>
+      <c r="B45" s="13"/>
+      <c r="C45" s="13"/>
       <c r="D45" s="9"/>
       <c r="E45" s="9"/>
       <c r="F45" s="9"/>
@@ -2988,9 +2992,9 @@
       <c r="AB45" s="9"/>
     </row>
     <row r="46" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="10"/>
-      <c r="B46" s="10"/>
-      <c r="C46" s="10"/>
+      <c r="A46" s="13"/>
+      <c r="B46" s="13"/>
+      <c r="C46" s="13"/>
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
       <c r="F46" s="9"/>
@@ -3018,9 +3022,9 @@
       <c r="AB46" s="9"/>
     </row>
     <row r="47" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="10"/>
-      <c r="B47" s="10"/>
-      <c r="C47" s="10"/>
+      <c r="A47" s="13"/>
+      <c r="B47" s="13"/>
+      <c r="C47" s="13"/>
       <c r="D47" s="9"/>
       <c r="E47" s="9"/>
       <c r="F47" s="9"/>
@@ -3048,9 +3052,9 @@
       <c r="AB47" s="9"/>
     </row>
     <row r="48" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="10"/>
-      <c r="B48" s="10"/>
-      <c r="C48" s="10"/>
+      <c r="A48" s="13"/>
+      <c r="B48" s="13"/>
+      <c r="C48" s="13"/>
       <c r="D48" s="9"/>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
@@ -3078,9 +3082,9 @@
       <c r="AB48" s="9"/>
     </row>
     <row r="49" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="10"/>
-      <c r="B49" s="10"/>
-      <c r="C49" s="10"/>
+      <c r="A49" s="13"/>
+      <c r="B49" s="13"/>
+      <c r="C49" s="13"/>
       <c r="D49" s="9"/>
       <c r="E49" s="9"/>
       <c r="F49" s="9"/>
@@ -3108,9 +3112,9 @@
       <c r="AB49" s="9"/>
     </row>
     <row r="50" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="10"/>
-      <c r="B50" s="10"/>
-      <c r="C50" s="10"/>
+      <c r="A50" s="13"/>
+      <c r="B50" s="13"/>
+      <c r="C50" s="13"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
@@ -3138,9 +3142,9 @@
       <c r="AB50" s="1"/>
     </row>
     <row r="51" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="10"/>
-      <c r="B51" s="10"/>
-      <c r="C51" s="10"/>
+      <c r="A51" s="13"/>
+      <c r="B51" s="13"/>
+      <c r="C51" s="13"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
@@ -3168,9 +3172,9 @@
       <c r="AB51" s="1"/>
     </row>
     <row r="52" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="10"/>
-      <c r="B52" s="10"/>
-      <c r="C52" s="10"/>
+      <c r="A52" s="13"/>
+      <c r="B52" s="13"/>
+      <c r="C52" s="13"/>
       <c r="D52" s="1"/>
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
@@ -3198,9 +3202,9 @@
       <c r="AB52" s="1"/>
     </row>
     <row r="53" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="10"/>
-      <c r="B53" s="10"/>
-      <c r="C53" s="10"/>
+      <c r="A53" s="13"/>
+      <c r="B53" s="13"/>
+      <c r="C53" s="13"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
@@ -3373,26 +3377,25 @@
       <c r="AA58" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="18">
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A50:C52"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A42:C44"/>
+    <mergeCell ref="A46:C48"/>
+    <mergeCell ref="A18:C24"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A2:C8"/>
+    <mergeCell ref="A10:C16"/>
     <mergeCell ref="A40:C40"/>
     <mergeCell ref="A26:C32"/>
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="A33:C35"/>
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="A37:C39"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A18:C24"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A2:C8"/>
-    <mergeCell ref="A10:C16"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A50:C52"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A42:C44"/>
-    <mergeCell ref="A46:C48"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
